--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ALABAMA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ALABAMA_2019.xlsx
@@ -607,7 +607,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="15">
@@ -1003,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="37">
@@ -1489,7 +1489,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="64">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C106">
@@ -2731,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="133">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C149">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C239">
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="291">
@@ -5971,7 +5971,7 @@
         <v>67</v>
       </c>
       <c r="D312">
-        <v>0.009123093681917211</v>
+        <v>0.009123093681917212</v>
       </c>
     </row>
     <row r="313">
@@ -5989,7 +5989,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="314">
@@ -6727,7 +6727,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="355">
@@ -7645,7 +7645,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="406">
@@ -7951,7 +7951,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="423">
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="427">
@@ -8239,7 +8239,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="439">
@@ -9787,7 +9787,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="525">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C603">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C619">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C621">
@@ -11857,7 +11857,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="640">
@@ -14089,7 +14089,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="764">
@@ -15223,7 +15223,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="827">
@@ -15295,7 +15295,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="831">
@@ -16015,7 +16015,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="871">
@@ -16735,7 +16735,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="911">
@@ -17059,7 +17059,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="929">
@@ -17131,7 +17131,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="933">
@@ -17599,7 +17599,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>0.0009531590413943355</v>
+        <v>0.0009531590413943356</v>
       </c>
     </row>
     <row r="959">
